--- a/Button Code.xlsx
+++ b/Button Code.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/caf7df62f197fd7d/GitHub/ga_suche/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{8BD1E9A8-4607-4CC2-A8B1-018BFDA227DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03D40557-E081-458D-81FE-A0A088484057}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="8_{8BD1E9A8-4607-4CC2-A8B1-018BFDA227DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C17AFB2-2E26-4980-93ED-B5D61001CECC}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" activeTab="1" xr2:uid="{00A3BA09-8961-4D07-A25D-F6AEBA4FFD2B}"/>
+    <workbookView xWindow="0" yWindow="1776" windowWidth="23040" windowHeight="11184" activeTab="1" xr2:uid="{00A3BA09-8961-4D07-A25D-F6AEBA4FFD2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -243,9 +243,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>✓</t>
-  </si>
-  <si>
     <t>GA/chronologisch</t>
   </si>
   <si>
@@ -279,9 +276,6 @@
     <t>Themen/Karten</t>
   </si>
   <si>
-    <t>✓(#)</t>
-  </si>
-  <si>
     <t>Nach Klick → Text (r. Panel)</t>
   </si>
   <si>
@@ -291,18 +285,9 @@
     <t>Ohne Ergebnis</t>
   </si>
   <si>
-    <t>✓(*)</t>
-  </si>
-  <si>
-    <t>✓(***)</t>
-  </si>
-  <si>
     <t>Themen/Sammlungen</t>
   </si>
   <si>
-    <t>✓(##)</t>
-  </si>
-  <si>
     <t>(##)</t>
   </si>
   <si>
@@ -318,7 +303,22 @@
     <t>(***)</t>
   </si>
   <si>
-    <t>✓(**)</t>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>ok(*)</t>
+  </si>
+  <si>
+    <t>ok(**)</t>
+  </si>
+  <si>
+    <t>ok(***)</t>
+  </si>
+  <si>
+    <t>ok(##)</t>
+  </si>
+  <si>
+    <t>ok(#)</t>
   </si>
 </sst>
 </file>
@@ -1818,12 +1818,12 @@
       <c r="F2" s="14"/>
       <c r="G2" s="14"/>
       <c r="H2" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>43</v>
@@ -1834,12 +1834,12 @@
       <c r="F3" s="14"/>
       <c r="G3" s="14"/>
       <c r="H3" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>43</v>
@@ -1850,7 +1850,7 @@
       <c r="F4" s="14"/>
       <c r="G4" s="14"/>
       <c r="H4" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -1858,7 +1858,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -1866,7 +1866,7 @@
       <c r="F5" s="14"/>
       <c r="G5" s="14"/>
       <c r="H5" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -1874,33 +1874,33 @@
         <v>10</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>49</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>50</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -1908,33 +1908,33 @@
       <c r="F7" s="14"/>
       <c r="G7" s="14"/>
       <c r="H7" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -1942,7 +1942,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -1950,7 +1950,7 @@
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
       <c r="H9" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -1958,68 +1958,68 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
       <c r="H11" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -2027,17 +2027,17 @@
         <v>19</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
       <c r="H13" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -2045,80 +2045,80 @@
         <v>19</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
       <c r="E16" s="14" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
       <c r="H16" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>55</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>57</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
       <c r="E17" s="14" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -2126,7 +2126,7 @@
         <v>26</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
@@ -2134,7 +2134,7 @@
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
       <c r="H18" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -2142,19 +2142,19 @@
         <v>26</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
       <c r="E19" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F19" s="14"/>
       <c r="G19" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -2162,7 +2162,7 @@
         <v>28</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -2170,7 +2170,7 @@
       <c r="F20" s="14"/>
       <c r="G20" s="14"/>
       <c r="H20" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -2178,35 +2178,35 @@
         <v>28</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
       <c r="E21" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F21" s="14"/>
       <c r="G21" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -2227,7 +2227,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>33</v>
